--- a/xls/square_16_tri3_15.xlsx
+++ b/xls/square_16_tri3_15.xlsx
@@ -482,13 +482,13 @@
         <v>1350</v>
       </c>
       <c r="I15">
-        <v>0.19699700153546718</v>
+        <v>0.19699703927398335</v>
       </c>
       <c r="J15">
-        <v>-2.0629737343686743</v>
+        <v>-2.062973631833059</v>
       </c>
       <c r="K15">
-        <v>-0.9821412634818097</v>
+        <v>-0.9821413729932267</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -517,13 +517,13 @@
         <v>1536</v>
       </c>
       <c r="I16">
-        <v>-2.3986342620214995</v>
+        <v>-2.398634237089755</v>
       </c>
       <c r="J16">
-        <v>-2.0999377265118544</v>
+        <v>-2.099937707517993</v>
       </c>
       <c r="K16">
-        <v>-1.5935997805697282</v>
+        <v>-1.5935997001126783</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -552,13 +552,13 @@
         <v>1734</v>
       </c>
       <c r="I17">
-        <v>-2.394093258305097</v>
+        <v>-2.394092740986117</v>
       </c>
       <c r="J17">
-        <v>-2.108079352074974</v>
+        <v>-2.1080792453242307</v>
       </c>
       <c r="K17">
-        <v>-0.5395560045882362</v>
+        <v>-0.5395405035491667</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -587,13 +587,13 @@
         <v>1944</v>
       </c>
       <c r="I18">
-        <v>-2.381239844647588</v>
+        <v>-2.3812400015276047</v>
       </c>
       <c r="J18">
-        <v>-2.0948862931672676</v>
+        <v>-2.094886448293044</v>
       </c>
       <c r="K18">
-        <v>0.07474248672133847</v>
+        <v>0.07467929729966509</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -622,13 +622,13 @@
         <v>2166</v>
       </c>
       <c r="I19">
-        <v>-2.3190089312089985</v>
+        <v>-2.3190095946528957</v>
       </c>
       <c r="J19">
-        <v>-1.8589336417124718</v>
+        <v>-1.8589338331898468</v>
       </c>
       <c r="K19">
-        <v>2.3494864819242927</v>
+        <v>2.3494862965416536</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -657,13 +657,13 @@
         <v>2400</v>
       </c>
       <c r="I20">
-        <v>-1.6597507606727604</v>
+        <v>-1.6597513717344297</v>
       </c>
       <c r="J20">
-        <v>-1.3680677678864364</v>
+        <v>-1.3680679389379318</v>
       </c>
       <c r="K20">
-        <v>3.3527473264142027</v>
+        <v>3.3527473368488785</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -692,13 +692,13 @@
         <v>2646</v>
       </c>
       <c r="I21">
-        <v>-0.6580064775926355</v>
+        <v>-0.6580064854207804</v>
       </c>
       <c r="J21">
-        <v>-0.6435878712179277</v>
+        <v>-0.6435878796241976</v>
       </c>
       <c r="K21">
-        <v>3.8219079138202847</v>
+        <v>3.8219079169914263</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -727,13 +727,13 @@
         <v>2904</v>
       </c>
       <c r="I22">
-        <v>-0.08331005496106206</v>
+        <v>-0.08331005610515778</v>
       </c>
       <c r="J22">
-        <v>-0.06719561166108423</v>
+        <v>-0.06719561250260465</v>
       </c>
       <c r="K22">
-        <v>3.753496155270232</v>
+        <v>3.75349615964993</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -762,13 +762,13 @@
         <v>3174</v>
       </c>
       <c r="I23">
-        <v>0.0010484255705950896</v>
+        <v>0.0010484255853795259</v>
       </c>
       <c r="J23">
-        <v>0.00028623645573975305</v>
+        <v>0.00028623646230798935</v>
       </c>
       <c r="K23">
-        <v>2.797476282945678</v>
+        <v>2.797476285028026</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -797,13 +797,13 @@
         <v>3456</v>
       </c>
       <c r="I24">
-        <v>0.00011367337245732649</v>
+        <v>0.00011367337240844788</v>
       </c>
       <c r="J24">
-        <v>-2.636955432312258e-5</v>
+        <v>-2.6369554290140582e-5</v>
       </c>
       <c r="K24">
-        <v>2.5904984485776215</v>
+        <v>2.5904984481077213</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -832,13 +832,13 @@
         <v>3750</v>
       </c>
       <c r="I25">
-        <v>4.963334011325693e-5</v>
+        <v>4.96333404867947e-5</v>
       </c>
       <c r="J25">
-        <v>-2.989776271649985e-5</v>
+        <v>-2.9897762565041798e-5</v>
       </c>
       <c r="K25">
-        <v>2.5005899056655982</v>
+        <v>2.5005899058621757</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -867,13 +867,13 @@
         <v>4056</v>
       </c>
       <c r="I26">
-        <v>1.1997600414206028e-5</v>
+        <v>1.1997600476499862e-5</v>
       </c>
       <c r="J26">
-        <v>-3.346346397549032e-5</v>
+        <v>-3.3463463957552445e-5</v>
       </c>
       <c r="K26">
-        <v>2.4396065436116525</v>
+        <v>2.4396065437605525</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -902,13 +902,13 @@
         <v>4374</v>
       </c>
       <c r="I27">
-        <v>-2.0535162300759877e-5</v>
+        <v>-2.0535162136286052e-5</v>
       </c>
       <c r="J27">
-        <v>-5.151894221390575e-5</v>
+        <v>-5.1518942128986645e-5</v>
       </c>
       <c r="K27">
-        <v>2.452741973730969</v>
+        <v>2.4527419739930645</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -937,13 +937,13 @@
         <v>4704</v>
       </c>
       <c r="I28">
-        <v>3.946063906827701e-6</v>
+        <v>3.946063860347539e-6</v>
       </c>
       <c r="J28">
-        <v>-4.215935136648701e-5</v>
+        <v>-4.215935138283395e-5</v>
       </c>
       <c r="K28">
-        <v>2.4536359546679525</v>
+        <v>2.453635954656985</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -972,13 +972,13 @@
         <v>5046</v>
       </c>
       <c r="I29">
-        <v>8.25393544216697e-5</v>
+        <v>8.253935443651752e-5</v>
       </c>
       <c r="J29">
-        <v>2.0222857484079348e-5</v>
+        <v>2.022285748716505e-5</v>
       </c>
       <c r="K29">
-        <v>2.308312119468862</v>
+        <v>2.308312119519099</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -1007,13 +1007,13 @@
         <v>5400</v>
       </c>
       <c r="I30">
-        <v>-5.360117406564374e-5</v>
+        <v>-5.360117405686728e-5</v>
       </c>
       <c r="J30">
-        <v>-3.228653218993245e-5</v>
+        <v>-3.2286532184869356e-5</v>
       </c>
       <c r="K30">
-        <v>1.8951161142507116</v>
+        <v>1.8951161142720687</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -1042,13 +1042,13 @@
         <v>5766</v>
       </c>
       <c r="I31">
-        <v>-2.06884062820616e-7</v>
+        <v>-2.068840627723996e-7</v>
       </c>
       <c r="J31">
         <v>-2.6651629532834066e-7</v>
       </c>
       <c r="K31">
-        <v>1.2252153720964887</v>
+        <v>1.2252153722565022</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -1077,13 +1077,13 @@
         <v>6144</v>
       </c>
       <c r="I32">
-        <v>-9.378848350139956e-7</v>
+        <v>-9.378848349657791e-7</v>
       </c>
       <c r="J32">
-        <v>-7.603509720402582e-7</v>
+        <v>-7.603509721849075e-7</v>
       </c>
       <c r="K32">
-        <v>1.320415337289966</v>
+        <v>1.3204153370816782</v>
       </c>
     </row>
   </sheetData>

--- a/xls/square_16_tri3_15.xlsx
+++ b/xls/square_16_tri3_15.xlsx
@@ -456,6 +456,76 @@
         <v>10</v>
       </c>
     </row>
+    <row r="13" spans="1:11">
+      <c r="A13" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13">
+        <v>256</v>
+      </c>
+      <c r="C13" t="s">
+        <v>11</v>
+      </c>
+      <c r="D13">
+        <v>289</v>
+      </c>
+      <c r="E13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F13">
+        <v>196</v>
+      </c>
+      <c r="G13" t="s">
+        <v>13</v>
+      </c>
+      <c r="H13">
+        <v>1014</v>
+      </c>
+      <c r="I13">
+        <v>3.7801787666213826</v>
+      </c>
+      <c r="J13">
+        <v>0.28471211310567646</v>
+      </c>
+      <c r="K13">
+        <v>1.2093259169845614</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14">
+        <v>256</v>
+      </c>
+      <c r="C14" t="s">
+        <v>11</v>
+      </c>
+      <c r="D14">
+        <v>289</v>
+      </c>
+      <c r="E14" t="s">
+        <v>12</v>
+      </c>
+      <c r="F14">
+        <v>225</v>
+      </c>
+      <c r="G14" t="s">
+        <v>13</v>
+      </c>
+      <c r="H14">
+        <v>1176</v>
+      </c>
+      <c r="I14">
+        <v>2.652940533684612</v>
+      </c>
+      <c r="J14">
+        <v>-0.5125418916532302</v>
+      </c>
+      <c r="K14">
+        <v>0.6496780892943274</v>
+      </c>
+    </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
         <v>11</v>
